--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J210-SpecialiteOrdinale-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J210-SpecialiteOrdinale-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="237">
   <si>
     <t>Property</t>
   </si>
@@ -139,24 +139,6 @@
   </si>
   <si>
     <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
-  </si>
-  <si>
-    <t>SI05</t>
-  </si>
-  <si>
-    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
-  </si>
-  <si>
-    <t>SI06</t>
-  </si>
-  <si>
-    <t>Infirmier(ère) de bloc opératoire (SI)</t>
-  </si>
-  <si>
-    <t>SI07</t>
-  </si>
-  <si>
-    <t>Infirmier(ère) anesthésiste (SI)</t>
   </si>
   <si>
     <t>SI08</t>
@@ -1003,7 +985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1847,39 +1829,15 @@
         <v>234</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
